--- a/examples/demo-company/reports/financial_statements.xlsx
+++ b/examples/demo-company/reports/financial_statements.xlsx
@@ -11,7 +11,10 @@
     <sheet name="Profit and Loss" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Cash Flow" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ratios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PPE reconciliation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ratios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Tax" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MSME dues" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +26,21 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##,##0.00;(#,##,##0.00);-"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,11 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -437,263 +450,226 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Sahyadri Trading Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CIN: U51909MH2019PTC123456 | Financial year 2025-26 | Amounts in Rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Particulars</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>31-03-2025</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>I. EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>(1) Shareholders' funds</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Share capital</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Reserves and surplus</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1057446.34</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>343129</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>(3) Non-current liabilities</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Long-term borrowings</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>500000</v>
-      </c>
+          <t>(1) Shareholders' funds</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Deferred tax liabilities (net)</t>
+          <t xml:space="preserve">    Share capital</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>6871</v>
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1000000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(4) Current liabilities</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t xml:space="preserve">    Reserves and surplus</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1057445.34</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>343129</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Trade payables - total outstanding dues of micro and small enterprises</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>354000</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>200000</v>
-      </c>
+          <t>(3) Non-current liabilities</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Other current liabilities</t>
+          <t xml:space="preserve">    Long-term borrowings</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>166400</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>500000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Short-term provisions</t>
+          <t xml:space="preserve">    Deferred tax liabilities (net)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>260119</v>
-      </c>
-      <c r="D12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="D12" s="4" t="n">
+        <v>6871</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="3" t="n">
-        <v>3337965.34</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>2050000</v>
-      </c>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>(4) Current liabilities</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>II. ASSETS</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr"/>
-      <c r="D14" s="1" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Trade payables - total outstanding dues of micro and small enterprises</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>354000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>200000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>(1) Non-current assets</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t xml:space="preserve">    Other current liabilities</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>166400</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Property, plant and equipment</t>
+          <t xml:space="preserve">    Short-term provisions</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>276269.95</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>300000</v>
+        <v>8</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>260120</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Deferred tax assets (net)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>8295.389999999999</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>0</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>3337965.34</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2050000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Long-term loans and advances</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>100000</v>
-      </c>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>II. ASSETS</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(2) Current assets</t>
+          <t>(1) Non-current assets</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -703,78 +679,136 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Inventories</t>
+          <t xml:space="preserve">    Property, plant and equipment</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>550000</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>400000</v>
+        <v>9</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>276269.95</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Trade receivables</t>
+          <t xml:space="preserve">    Deferred tax assets (net)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>598400</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>300000</v>
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>8295.389999999999</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Cash and cash equivalents</t>
+          <t xml:space="preserve">    Long-term loans and advances</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>1392100</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>950000</v>
+        <v>11</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>(2) Current assets</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Inventories</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>550000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Trade receivables</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>13</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>598400</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>1392100</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t xml:space="preserve">    Other current assets</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B27" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C27" s="4" t="n">
         <v>412900</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D27" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="3" t="n">
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
         <v>3337965.34</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D28" s="5" t="n">
         <v>2050000</v>
       </c>
     </row>
@@ -789,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -801,240 +835,261 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Sahyadri Trading Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CIN: U51909MH2019PTC123456 | Financial year 2025-26 | Amounts in Rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Profit and Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Particulars</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>31-03-2025</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>I. Revenue from operations</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>4540000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>II. Other income</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>III. Total income (I + II)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" s="2" t="n">
-        <v>4548000</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>IV. Expenses:</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Purchases of stock-in-trade</t>
+          <t>I. Revenue from operations</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2100000</v>
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>4540000</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Changes in inventories of finished goods, work-in-progress and stock-in-trade</t>
+          <t>II. Other income</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>-150000</v>
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>8000</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Employee benefits expense</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>741000</v>
+          <t>III. Total income (I + II)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" s="4" t="n">
+        <v>4548000</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Depreciation and amortisation expense</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>123730.05</v>
-      </c>
+          <t>IV. Expenses:</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other expenses</t>
+          <t xml:space="preserve">  Purchases of stock-in-trade</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>774000</v>
+        <v>18</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2100000</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total expenses (IV)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" s="2" t="n">
-        <v>3588730.05</v>
+          <t xml:space="preserve">  Changes in inventories of finished goods, work-in-progress and stock-in-trade</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-150000</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. Profit before exceptional items and tax (III - IV)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" s="2" t="n">
-        <v>959269.95</v>
+          <t xml:space="preserve">  Employee benefits expense</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>741000</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VI. Exceptional items</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" s="2" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  Depreciation and amortisation expense</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>21</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>123730.05</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VII. Profit before tax (V - VI)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" s="2" t="n">
-        <v>959269.95</v>
+          <t xml:space="preserve">  Other expenses</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>22</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>774000</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VIII. Tax expense: (1) Current tax</t>
+          <t>Total expenses (IV)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" s="2" t="n">
-        <v>260119</v>
+      <c r="C15" s="4" t="n">
+        <v>3588730.05</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2) Deferred tax</t>
+          <t>V. Profit before exceptional items and tax (III - IV)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" s="2" t="n">
-        <v>-15166.39</v>
+      <c r="C16" s="4" t="n">
+        <v>959269.95</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IX. Profit/(loss) for the year (VII - VIII)</t>
+          <t>VI. Exceptional items</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" s="2" t="n">
-        <v>714317.34</v>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>VII. Profit before tax (V - VI)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" s="4" t="n">
+        <v>959269.95</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VIII. Tax expense: (1) Current tax</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" s="4" t="n">
+        <v>260120</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (2) Deferred tax</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" s="4" t="n">
+        <v>-15166.39</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IX. Profit/(loss) for the year (VII - VIII)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" s="4" t="n">
+        <v>714316.34</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>X. Earnings per equity share (face value Rs 10): basic and diluted</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" s="2" t="n">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1047,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1057,75 +1112,58 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Sahyadri Trading Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CIN: U51909MH2019PTC123456 | Financial year 2025-26 | Amounts in Rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Cash Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Particulars</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A. Cash flow from operating activities</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Net profit before tax</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>959269.95</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Adjustments for:</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>123730.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Interest income</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>-8000</v>
-      </c>
+          <t>A. Cash flow from operating activities</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Operating profit before working capital changes</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>1075000</v>
+          <t xml:space="preserve">  Net profit before tax</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>959269.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Working capital changes:</t>
+          <t>Adjustments for:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -1133,125 +1171,125 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase/(decrease) in trade payables - total outstanding dues of micro and small enterprises</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>154000</v>
+          <t xml:space="preserve">  Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>123730.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase/(decrease) in other current liabilities</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>166400</v>
+          <t xml:space="preserve">  Interest income</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>-8000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase)/decrease in inventories</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>-150000</v>
+          <t xml:space="preserve">  Operating profit before working capital changes</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1075000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase)/decrease in trade receivables</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>-298400</v>
-      </c>
+          <t>Working capital changes:</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase)/decrease in other current assets</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>-162900</v>
+          <t xml:space="preserve">  Increase/(decrease) in trade payables - total outstanding dues of micro and small enterprises</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>154000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash generated from operations</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>784100</v>
+          <t xml:space="preserve">  Increase/(decrease) in other current liabilities</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>166400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Income taxes paid (net of refunds)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>-250000</v>
+          <t xml:space="preserve">  (Increase)/decrease in inventories</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>-150000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Net cash from operating activities (A)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>534100</v>
+          <t xml:space="preserve">  (Increase)/decrease in trade receivables</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>-298400</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. Cash flow from investing activities</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t xml:space="preserve">  (Increase)/decrease in other current assets</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>-162900</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Purchase of property, plant and equipment and intangibles (net of disposals)</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>-100000</v>
+          <t xml:space="preserve">  Cash generated from operations</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>784100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Interest received</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>8000</v>
+          <t xml:space="preserve">  Income taxes paid (net of refunds)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>-250000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities (B)</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>-92000</v>
+          <t>Net cash from operating activities (A)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>534100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. Cash flow from financing activities</t>
+          <t>B. Cash flow from investing activities</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1259,40 +1297,78 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Net cash from financing activities (C)</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  Purchase of property, plant and equipment and intangibles (net of disposals)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>-100000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Net increase/(decrease) in cash and cash equivalents (A+B+C)</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>442100</v>
+          <t xml:space="preserve">  Interest received</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at the beginning of the year</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>950000</v>
+          <t>Net cash used in investing activities (B)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>-92000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>C. Cash flow from financing activities</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Net cash from financing activities (C)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Net increase/(decrease) in cash and cash equivalents (A+B+C)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>442100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at the beginning of the year</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Cash and cash equivalents at the end of the year</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B29" s="4" t="n">
         <v>1392100</v>
       </c>
     </row>
@@ -1307,12 +1383,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1320,231 +1396,176 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Sahyadri Trading Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CIN: U51909MH2019PTC123456 | Financial year 2025-26 | Amounts in Rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>31-03-2025</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Equity Share Capital</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Reserves and surplus</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Surplus in Statement of Profit and Loss</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>343129</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>343129</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Reserves and surplus</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Profit/(loss) for the year</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>714317.34</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Long-term borrowings</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Unsecured Loans from Directors</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>500000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deferred tax liabilities (net)</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability (Net)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6871</v>
+          <t>Equity Share Capital</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1000000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trade payables - total outstanding dues of micro and small enterprises</t>
+          <t>Reserves and surplus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rathod Components Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>354000</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>200000</v>
+          <t>Surplus in Statement of Profit and Loss</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>343129</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>343129</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other current liabilities</t>
+          <t>Reserves and surplus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Audit Fees Payable</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>714316.34</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other current liabilities</t>
+          <t>Long-term borrowings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RCM CGST Payable</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>54450</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Unsecured Loans from Directors</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>500000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other current liabilities</t>
+          <t>Deferred tax liabilities (net)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RCM SGST Payable</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>54450</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Deferred Tax Liability (Net)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>6871</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other current liabilities</t>
+          <t>Trade payables - total outstanding dues of micro and small enterprises</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TDS Payable - 192 Salary</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Rathod Components Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>354000</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>200000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1557,542 +1578,542 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TDS Payable - 194I Rent</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>5500</v>
+          <t>Audit Fees Payable</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>50000</v>
       </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Short-term provisions</t>
+          <t>Other current liabilities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Provision for Income Tax</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>260119</v>
+          <t>RCM CGST Payable</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>54450</v>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Other current liabilities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Computers</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>150000</v>
-      </c>
+          <t>RCM SGST Payable</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>54450</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Other current liabilities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Furniture and Fixtures</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>300000</v>
-      </c>
+          <t>TDS Payable - 192 Salary</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Other current liabilities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Computers</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>-151602.32</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>-90000</v>
-      </c>
+          <t>TDS Payable - 194I Rent</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Short-term provisions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Furniture and Fixtures</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>-122127.73</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>-60000</v>
-      </c>
+          <t>Provision for Income Tax</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>260120</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deferred tax assets (net)</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability (Net)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>8295.389999999999</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>Computers</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>150000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Long-term loans and advances</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Security Deposits</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>100000</v>
+          <t>Furniture and Fixtures</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Inventories</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stock-in-Trade</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>550000</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>400000</v>
+          <t>Accumulated Depreciation - Computers</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-151602.32</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-90000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trade receivables</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Patil Retail LLP</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>598400</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>300000</v>
+          <t>Accumulated Depreciation - Furniture and Fixtures</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-122127.73</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-60000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
+          <t>Deferred tax assets (net)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cash in Hand</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>55200</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>50000</v>
-      </c>
+          <t>Deferred Tax Liability (Net) (debit balance, shown as a deferred tax asset)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>8295.389999999999</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
+          <t>Long-term loans and advances</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HDFC Bank Current A/c</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>1336900</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>900000</v>
+          <t>Security Deposits</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Advance Tax</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Stock-in-Trade</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>550000</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>400000</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Trade receivables</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Input CGST</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>54450</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>Patil Retail LLP</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>598400</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>300000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Input IGST</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>54000</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Cash in Hand</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>55200</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>50000</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Other current assets</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Input SGST</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>54450</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>HDFC Bank Current A/c</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1336900</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>900000</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Revenue from operations</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Export Sales</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>400000</v>
+          <t>Advance Tax</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>250000</v>
       </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Revenue from operations</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sales - Goods</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>4140000</v>
+          <t>Input CGST</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>54450</v>
       </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>8000</v>
+          <t>Input IGST</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>54000</v>
       </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Purchases of stock-in-trade</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Purchases - Stock-in-Trade</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>2100000</v>
+          <t>Input SGST</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>54450</v>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Changes in inventories of finished goods, work-in-progress and stock-in-trade</t>
+          <t>Revenue from operations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Changes in Inventories</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>-150000</v>
+          <t>Export Sales</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>400000</v>
       </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Employee benefits expense</t>
+          <t>Revenue from operations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salaries and Wages</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>720000</v>
+          <t>Sales - Goods</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>4140000</v>
       </c>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Employee benefits expense</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Staff Welfare Expenses</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>21000</v>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>8000</v>
       </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation expense</t>
+          <t>Purchases of stock-in-trade</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>123730.05</v>
+          <t>Purchases - Stock-in-Trade</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>2100000</v>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Changes in inventories of finished goods, work-in-progress and stock-in-trade</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Consumables and Packing Material</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>50000</v>
+          <t>Changes in Inventories</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>-150000</v>
       </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Employee benefits expense</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Payment to Auditors - Statutory Audit</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>50000</v>
+          <t>Salaries and Wages</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>720000</v>
       </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Employee benefits expense</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Penalties and Fines</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>2000</v>
+          <t>Staff Welfare Expenses</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>21000</v>
       </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Depreciation and amortisation expense</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>660000</v>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>123730.05</v>
       </c>
       <c r="E39" t="inlineStr"/>
     </row>
@@ -2107,13 +2128,89 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>Consumables and Packing Material</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>22</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Payment to Auditors - Statutory Audit</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>22</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Penalties and Fines</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>22</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>660000</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>22</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>Repairs and Maintenance - Others</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D44" s="4" t="n">
         <v>12000</v>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2126,7 +2223,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sahyadri Trading Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CIN: U51909MH2019PTC123456 | Financial year 2025-26 | Amounts in Rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>PPE reconciliation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Additions / charge</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Disposals / on disposals</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gross block</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Computers</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gross block</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Furniture and Fixtures</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Accumulated depreciation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Computers</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>61602.32</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>151602.32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Accumulated depreciation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Furniture and Fixtures</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>62127.73</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>122127.73</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Net block</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" s="4" t="n">
+        <v>276269.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2138,113 +2453,469 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Sahyadri Trading Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CIN: U51909MH2019PTC123456 | Financial year 2025-26 | Amounts in Rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ratios</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>Ratio</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Previous</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Variance %</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Current ratio</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Debt-equity ratio</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Return on equity (%)</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>42.01</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Inventory turnover</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trade receivables turnover</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>10.11</v>
+          <t>Current ratio</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>3.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trade payables turnover</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>7.58</v>
+          <t>Debt-equity ratio</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Net capital turnover</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>2.09</v>
+          <t>Return on equity (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>42.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net profit ratio (%)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>15.73</v>
+          <t>Inventory turnover</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>4.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Trade receivables turnover</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>10.11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Trade payables turnover</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Net capital turnover</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net profit ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>15.73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Return on capital employed (%)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B14" s="4" t="n">
         <v>37.51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sahyadri Trading Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CIN: U51909MH2019PTC123456 | Financial year 2025-26 | Amounts in Rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Particulars</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>959269.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Current tax</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>260120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Deferred tax</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>-15166.39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total tax expense</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>244953.61</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Effective tax rate (%)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>25.54</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Provision for income tax (closing)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>260120</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Less: advance tax, TDS/TCS and self-assessment tax (closing)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net tax payable / (refundable)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>10120</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Deferred tax liability / (asset), opening</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>6871</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Charge / (credit) to profit and loss</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>-15166.39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Deferred tax liability / (asset), closing</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>-8295.389999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Income-tax computation (working/tax_computation.json)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1033530</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tax liability</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>260120</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Interest u/s 234A/B/C</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Balance payable / (refund)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>12050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sahyadri Trading Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CIN: U51909MH2019PTC123456 | Financial year 2025-26 | Amounts in Rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>MSME dues</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Bill / ref</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Age (days)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Pay by (15 days)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Pay by (45 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rathod Components Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RC/240</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>354000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
       </c>
     </row>
   </sheetData>
